--- a/TestReport_20260422_140314.xlsx
+++ b/TestReport_20260422_140314.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baris\IdeaProjects\MuudSearchTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF68495-867F-41BA-B75D-7D703FC2C0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D359C4-176F-4061-AD49-D686EA1768E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3648,10 +3648,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3673,6 +3669,10 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4022,13 +4022,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4256,7 +4256,7 @@
       <c r="G15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="19" t="s">
         <v>1020</v>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       <c r="B21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="23" t="s">
         <v>56</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -4397,7 +4397,7 @@
       <c r="G21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="21" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       <c r="B28" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="23" t="s">
         <v>85</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -4561,7 +4561,7 @@
       <c r="G28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="20" t="s">
         <v>1022</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       <c r="B33" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="23" t="s">
         <v>105</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -4679,7 +4679,7 @@
       <c r="G33" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="20" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       <c r="B40" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" s="23" t="s">
         <v>133</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -4843,7 +4843,7 @@
       <c r="G40" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H40" s="22" t="s">
+      <c r="H40" s="20" t="s">
         <v>1023</v>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       <c r="B41" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="23" t="s">
         <v>137</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -4869,8 +4869,8 @@
       <c r="G41" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H41" s="23" t="s">
-        <v>1023</v>
+      <c r="H41" s="21" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="114.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4895,7 +4895,7 @@
       <c r="G42" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H42" s="22" t="s">
+      <c r="H42" s="20" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       <c r="G43" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H43" s="23" t="s">
+      <c r="H43" s="21" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       <c r="B57" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="23" t="s">
         <v>201</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -5370,7 +5370,7 @@
       <c r="G62" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="20" t="s">
         <v>1031</v>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       <c r="G63" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H63" s="23" t="s">
+      <c r="H63" s="21" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       <c r="G75" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="H75" s="23" t="s">
+      <c r="H75" s="21" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       <c r="G84" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="H84" s="22" t="s">
+      <c r="H84" s="20" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       <c r="G85" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H85" s="23"/>
+      <c r="H85" s="21"/>
     </row>
     <row r="86" spans="1:8" ht="114.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
@@ -5984,7 +5984,7 @@
       <c r="G88" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H88" s="22" t="s">
+      <c r="H88" s="20" t="s">
         <v>1024</v>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       <c r="E90" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F90" s="24" t="s">
+      <c r="F90" s="22" t="s">
         <v>37</v>
       </c>
       <c r="G90" s="2" t="s">
@@ -6067,7 +6067,7 @@
       <c r="B92" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C92" s="25" t="s">
+      <c r="C92" s="23" t="s">
         <v>337</v>
       </c>
       <c r="D92" s="2" t="s">
@@ -6332,7 +6332,7 @@
       <c r="B103" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C103" s="25" t="s">
+      <c r="C103" s="23" t="s">
         <v>377</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -6378,7 +6378,7 @@
       <c r="B105" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="C105" s="25" t="s">
+      <c r="C105" s="23" t="s">
         <v>385</v>
       </c>
       <c r="D105" s="3" t="s">
@@ -6393,7 +6393,7 @@
       <c r="G105" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="H105" s="23" t="s">
+      <c r="H105" s="21" t="s">
         <v>1032</v>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       <c r="B106" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C106" s="25" t="s">
+      <c r="C106" s="23" t="s">
         <v>389</v>
       </c>
       <c r="D106" s="2" t="s">
@@ -6427,7 +6427,7 @@
       <c r="B107" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="C107" s="25" t="s">
+      <c r="C107" s="23" t="s">
         <v>393</v>
       </c>
       <c r="D107" s="3" t="s">
@@ -6442,7 +6442,7 @@
       <c r="G107" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="H107" s="23" t="s">
+      <c r="H107" s="21" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       <c r="B111" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="C111" s="25" t="s">
+      <c r="C111" s="23" t="s">
         <v>409</v>
       </c>
       <c r="D111" s="3" t="s">
@@ -6568,7 +6568,7 @@
       <c r="B113" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="C113" s="25" t="s">
+      <c r="C113" s="23" t="s">
         <v>417</v>
       </c>
       <c r="D113" s="3" t="s">
@@ -6660,7 +6660,7 @@
       <c r="B117" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C117" s="25" t="s">
+      <c r="C117" s="23" t="s">
         <v>433</v>
       </c>
       <c r="D117" s="3" t="s">
@@ -6683,7 +6683,7 @@
       <c r="B118" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="C118" s="25" t="s">
+      <c r="C118" s="23" t="s">
         <v>437</v>
       </c>
       <c r="D118" s="2" t="s">
@@ -6722,14 +6722,14 @@
         <v>407</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="114.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" ht="114.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>105</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C120" s="26" t="s">
+      <c r="C120" s="24" t="s">
         <v>443</v>
       </c>
       <c r="D120" s="2" t="s">
@@ -6738,7 +6738,7 @@
       <c r="E120" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F120" s="27" t="s">
+      <c r="F120" s="25" t="s">
         <v>37</v>
       </c>
       <c r="G120" s="2" t="s">
@@ -6752,7 +6752,7 @@
       <c r="B121" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="C121" s="25" t="s">
+      <c r="C121" s="23" t="s">
         <v>409</v>
       </c>
       <c r="D121" s="3" t="s">
@@ -6798,7 +6798,7 @@
       <c r="B123" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="C123" s="25" t="s">
+      <c r="C123" s="23" t="s">
         <v>451</v>
       </c>
       <c r="D123" s="3" t="s">
@@ -6813,7 +6813,7 @@
       <c r="G123" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="H123" s="23" t="s">
+      <c r="H123" s="21" t="s">
         <v>1034</v>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       <c r="B125" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="C125" s="25" t="s">
+      <c r="C125" s="23" t="s">
         <v>457</v>
       </c>
       <c r="D125" s="3" t="s">
@@ -6870,7 +6870,7 @@
       <c r="B126" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C126" s="25" t="s">
+      <c r="C126" s="23" t="s">
         <v>461</v>
       </c>
       <c r="D126" s="2" t="s">
@@ -6893,7 +6893,7 @@
       <c r="B127" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C127" s="25" t="s">
+      <c r="C127" s="23" t="s">
         <v>465</v>
       </c>
       <c r="D127" s="3" t="s">
@@ -7345,7 +7345,7 @@
       <c r="G146" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="H146" s="22" t="s">
+      <c r="H146" s="20" t="s">
         <v>1035</v>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="114.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="114.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="3"/>
@@ -8078,7 +8078,7 @@
       <c r="B179" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="C179" s="25" t="s">
+      <c r="C179" s="23" t="s">
         <v>667</v>
       </c>
       <c r="D179" s="3" t="s">
@@ -8093,7 +8093,7 @@
       <c r="G179" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="H179" s="23" t="s">
+      <c r="H179" s="21" t="s">
         <v>1032</v>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       <c r="B183" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="C183" s="25" t="s">
+      <c r="C183" s="23" t="s">
         <v>683</v>
       </c>
       <c r="D183" s="3" t="s">
@@ -8426,7 +8426,7 @@
       <c r="B194" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="C194" s="25" t="s">
+      <c r="C194" s="23" t="s">
         <v>725</v>
       </c>
       <c r="D194" s="2" t="s">
@@ -8441,7 +8441,7 @@
       <c r="G194" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="H194" s="22" t="s">
+      <c r="H194" s="20" t="s">
         <v>1037</v>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       <c r="G196" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="H196" s="22" t="s">
+      <c r="H196" s="20" t="s">
         <v>1036</v>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       <c r="B200" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="C200" s="25" t="s">
+      <c r="C200" s="23" t="s">
         <v>749</v>
       </c>
       <c r="D200" s="2" t="s">
@@ -8616,7 +8616,7 @@
       <c r="B202" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="C202" s="25" t="s">
+      <c r="C202" s="23" t="s">
         <v>757</v>
       </c>
       <c r="D202" s="2" t="s">
@@ -8823,7 +8823,7 @@
       <c r="B211" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="C211" s="25" t="s">
+      <c r="C211" s="23" t="s">
         <v>793</v>
       </c>
       <c r="D211" s="3" t="s">
@@ -9582,7 +9582,7 @@
       <c r="B244" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="C244" s="25" t="s">
+      <c r="C244" s="23" t="s">
         <v>911</v>
       </c>
       <c r="D244" s="2" t="s">
@@ -9597,7 +9597,7 @@
       <c r="G244" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="H244" s="22" t="s">
+      <c r="H244" s="20" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       <c r="B263" s="4" t="s">
         <v>967</v>
       </c>
-      <c r="C263" s="25" t="s">
+      <c r="C263" s="23" t="s">
         <v>968</v>
       </c>
       <c r="D263" s="2" t="s">
@@ -10037,7 +10037,7 @@
       <c r="G263" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="H263" s="22" t="s">
+      <c r="H263" s="20" t="s">
         <v>1038</v>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       <c r="B272" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="C272" s="25" t="s">
+      <c r="C272" s="23" t="s">
         <v>1001</v>
       </c>
       <c r="D272" s="3" t="s">
@@ -10278,7 +10278,7 @@
       <c r="B274" s="5" t="s">
         <v>1008</v>
       </c>
-      <c r="C274" s="25" t="s">
+      <c r="C274" s="23" t="s">
         <v>1009</v>
       </c>
       <c r="D274" s="3" t="s">
@@ -10293,7 +10293,7 @@
       <c r="G274" s="3" t="s">
         <v>1011</v>
       </c>
-      <c r="H274" s="23" t="s">
+      <c r="H274" s="21" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       <c r="B275" s="4" t="s">
         <v>1012</v>
       </c>
-      <c r="C275" s="25" t="s">
+      <c r="C275" s="23" t="s">
         <v>1013</v>
       </c>
       <c r="D275" s="2" t="s">
